--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oj\leetcode\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
@@ -13,7 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3574</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3678</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14518" uniqueCount="6710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14990" uniqueCount="6899">
   <si>
     <t>名称</t>
   </si>
@@ -1019,7 +1024,8 @@
 如果是'('：leftBracket加一，并修正star为min(star, leftBracket)
 如果是'*'：star加一
 如果是')'：若leftBracket非0，leftBracket减一；若star非0，star减一；否则返回False
-遍历之后，返回leftBracket &lt;= star</t>
+遍历之后，返回leftBracket &lt;= star
+上面的方法是错误的，增加用例之后，不能通过，2026/10/4 修正了这个题解</t>
   </si>
   <si>
     <t>行星碰撞</t>
@@ -21659,6 +21665,593 @@
   </si>
   <si>
     <t>87(3600题)</t>
+  </si>
+  <si>
+    <t>创建一个恰好有 K 条路径的网格图 I</t>
+  </si>
+  <si>
+    <t>构造题+分类讨论</t>
+  </si>
+  <si>
+    <t>LCP 54</t>
+  </si>
+  <si>
+    <t>夺回据点</t>
+  </si>
+  <si>
+    <t>点双连通分量</t>
+  </si>
+  <si>
+    <t>Tarjan算法</t>
+  </si>
+  <si>
+    <t>网格中保持一致的最大列数</t>
+  </si>
+  <si>
+    <t>统计起止时间经过的秒数</t>
+  </si>
+  <si>
+    <t>处理所有元素的成本</t>
+  </si>
+  <si>
+    <t>模拟 + 等差数列求和</t>
+  </si>
+  <si>
+    <t>C++要注意求和公式输入要先求模</t>
+  </si>
+  <si>
+    <t>回文子数组求和</t>
+  </si>
+  <si>
+    <t>划分数组的最少相邻交换次数</t>
+  </si>
+  <si>
+    <t>灵神有更直接的定理</t>
+  </si>
+  <si>
+    <t>交替数列的最大元素</t>
+  </si>
+  <si>
+    <t>重新排列字符串以避免字符对</t>
+  </si>
+  <si>
+    <t>统计二叉树中支配节点的数量</t>
+  </si>
+  <si>
+    <t>字符串变换后的最少分组数</t>
+  </si>
+  <si>
+    <t>最小表示</t>
+  </si>
+  <si>
+    <t>一个小技巧，类似KMP</t>
+  </si>
+  <si>
+    <t>转换字符串的最小成本 III</t>
+  </si>
+  <si>
+    <t>暴力DP</t>
+  </si>
+  <si>
+    <t>偶数次骑士移动</t>
+  </si>
+  <si>
+    <t>可以用奇偶性判断</t>
+  </si>
+  <si>
+    <t>统计节点和为偶数的连通子图</t>
+  </si>
+  <si>
+    <t>使用子序列排序转换二进制字符串</t>
+  </si>
+  <si>
+    <t>正反两次遍历，分别验证两个方向各一种类型是否都能匹配完毕</t>
+  </si>
+  <si>
+    <t>设计 SQL</t>
+  </si>
+  <si>
+    <t>聚合两个时间序列</t>
+  </si>
+  <si>
+    <t>写法上有些技巧，从后向前逆序处理会方便一些</t>
+  </si>
+  <si>
+    <t>统计有效序列数目</t>
+  </si>
+  <si>
+    <t>组合数学+正难则反</t>
+  </si>
+  <si>
+    <t>计算序列中所有元素都是奇数的序列个数不容易想到</t>
+  </si>
+  <si>
+    <t>好子序列查询</t>
+  </si>
+  <si>
+    <t>思维题 + 线段树</t>
+  </si>
+  <si>
+    <t>思维难度很大</t>
+  </si>
+  <si>
+    <t>交替方向的最小路径代价 III</t>
+  </si>
+  <si>
+    <t>给定数位和的最大整数</t>
+  </si>
+  <si>
+    <t>移除子数组元素后第 K 小偶数</t>
+  </si>
+  <si>
+    <t>分类讨论 + 二分</t>
+  </si>
+  <si>
+    <t>思路不难想到，但写起来很复杂，下标很容易想错了</t>
+  </si>
+  <si>
+    <t>击败所有怪物的最小初始强度</t>
+  </si>
+  <si>
+    <t>差分数组 + 二分</t>
+  </si>
+  <si>
+    <t>购买苹果的最低成本 II</t>
+  </si>
+  <si>
+    <t>2n个Dijkstra</t>
+  </si>
+  <si>
+    <t>统计每个班次结束后的未完成任务数</t>
+  </si>
+  <si>
+    <t>模拟+二分</t>
+  </si>
+  <si>
+    <t>栅栏的最宽宽度</t>
+  </si>
+  <si>
+    <t>对于C++哈希这步是必须的</t>
+  </si>
+  <si>
+    <t>统计有效前缀数目</t>
+  </si>
+  <si>
+    <t>按奇偶比统计子数组 II</t>
+  </si>
+  <si>
+    <t>个人解法：有序数组</t>
+  </si>
+  <si>
+    <t>数对的最大强度</t>
+  </si>
+  <si>
+    <t>最小可整除数位乘积 II</t>
+  </si>
+  <si>
+    <t>思维 + 类数位DP</t>
+  </si>
+  <si>
+    <t>思考难度很大，实际是一道暴力搜索的题，用贪心不好做
+知道方法后，还有很多写法上的技巧和细节，容易少情况</t>
+  </si>
+  <si>
+    <t>LCP 58</t>
+  </si>
+  <si>
+    <t>积木拼接</t>
+  </si>
+  <si>
+    <t>回溯 + 模拟</t>
+  </si>
+  <si>
+    <t>思路上就是枚举所有可能，但适当的剪枝可以提高很多的性能
+1. 第一个面可以任意选定一个shape[i]的任何方向，不需要遍历第一块的各个方向，通过剩余块去迎合它即可
+2. 棱块和角块要分别计算，混在一起处理很麻烦
+3. 写法上的技巧，尽量用公共函数，面，棱，点的编号</t>
+  </si>
+  <si>
+    <t>两个不重叠子正方形的最大面积</t>
+  </si>
+  <si>
+    <t>二分 + 二维前缀和</t>
+  </si>
+  <si>
+    <t>前后缀分解也是一个方法</t>
+  </si>
+  <si>
+    <t>树的加权和</t>
+  </si>
+  <si>
+    <t>统计从两个字符串形成目标字符串的不同方案数</t>
+  </si>
+  <si>
+    <t>多维DP+方案数</t>
+  </si>
+  <si>
+    <t>这题状态设计比较难，状态设计的不同，可能对状态转移的设计有较大影响，容易多算</t>
+  </si>
+  <si>
+    <t>单调队列+双DP</t>
+  </si>
+  <si>
+    <t>这题的状态设计太难，设计之后，还有很技巧的状态转移思路，过于技巧性</t>
+  </si>
+  <si>
+    <t>应用折扣后的最低总价</t>
+  </si>
+  <si>
+    <t>数组中的峰值 II</t>
+  </si>
+  <si>
+    <t>能比较容易想到用线段树，不过线段树上维护的东西比较多，在区间合并时，写法上的细节也比较多，很容易出错，应该有更简洁的线段树写法</t>
+  </si>
+  <si>
+    <t>无限字符串里第 K 个数字</t>
+  </si>
+  <si>
+    <t>类似于模拟查找</t>
+  </si>
+  <si>
+    <t>工位的最大间隔</t>
+  </si>
+  <si>
+    <t>电梯请求 III</t>
+  </si>
+  <si>
+    <t>想到状压DP，状态设计没弄好，导致复杂度大了很多</t>
+  </si>
+  <si>
+    <t>得到旋转回文字符串的最少操作次数 I</t>
+  </si>
+  <si>
+    <t>交通灯的最大等待时间</t>
+  </si>
+  <si>
+    <t>电梯请求 II</t>
+  </si>
+  <si>
+    <t>想到区间DP，还是难在状态设计，另外还需要一个小优化</t>
+  </si>
+  <si>
+    <t>按奇偶比统计子数组 I</t>
+  </si>
+  <si>
+    <t>同4013题</t>
+  </si>
+  <si>
+    <t>最近的可用无人机</t>
+  </si>
+  <si>
+    <t>互质元素的最大得分</t>
+  </si>
+  <si>
+    <t>莫比乌斯函数+容斥原理</t>
+  </si>
+  <si>
+    <t>莫比乌斯函数是容斥原理的系数，有专门的求解方法，之前没有接触过</t>
+  </si>
+  <si>
+    <t>至多 K 个不同质因数集合的最长子数组</t>
+  </si>
+  <si>
+    <t>质因数分解 + 滑窗</t>
+  </si>
+  <si>
+    <t>找到所有数组中消失的数字 II</t>
+  </si>
+  <si>
+    <t>有效 K 个不同元素子数组 I</t>
+  </si>
+  <si>
+    <t>莫队 or 树状数组</t>
+  </si>
+  <si>
+    <t>普通的莫队就可以通过，开始用了回滚莫队为啥性能不够</t>
+  </si>
+  <si>
+    <t>电梯请求 I</t>
+  </si>
+  <si>
+    <t>判断 ASCII 值回文</t>
+  </si>
+  <si>
+    <t>M 个非重叠子数组最大和 I</t>
+  </si>
+  <si>
+    <t>DP + 优先队列优化</t>
+  </si>
+  <si>
+    <t>字符对转换后字典序最大的字符串</t>
+  </si>
+  <si>
+    <t>构造子集和的最少操作次数 II</t>
+  </si>
+  <si>
+    <t>构造子集和的最少操作次数 I</t>
+  </si>
+  <si>
+    <t>类似4041，这题简单点，一个数能转到的数只有自己的2^n倍和2^n分之一取整</t>
+  </si>
+  <si>
+    <t>解码值之和</t>
+  </si>
+  <si>
+    <t>象到达目标格子的最少移动步数</t>
+  </si>
+  <si>
+    <t>一步能到的两点，斜率只能是1或-1，一步走不到的点，两步一定能到
+自己做的时候，以为需要至多3步</t>
+  </si>
+  <si>
+    <t>最多有效分割位置 II</t>
+  </si>
+  <si>
+    <t>有点类似LogTrick</t>
+  </si>
+  <si>
+    <t>只需枚举可能导致前缀或后缀gcd变化的位置，还是比较难想到</t>
+  </si>
+  <si>
+    <t>最多有效分割位置 I</t>
+  </si>
+  <si>
+    <t>同4037题</t>
+  </si>
+  <si>
+    <t>计算单个区间中出现的整数数量</t>
+  </si>
+  <si>
+    <t>二分 + 反悔贪心</t>
+  </si>
+  <si>
+    <t>思维难度太大，有多个中间结论</t>
+  </si>
+  <si>
+    <t>LCP 59</t>
+  </si>
+  <si>
+    <t>搭桥过河</t>
+  </si>
+  <si>
+    <t>M 个非重叠子数组最大和 II</t>
+  </si>
+  <si>
+    <t>WQS二分</t>
+  </si>
+  <si>
+    <t>思考的难度太大，写法上也有很多细节
+没有 m 约束时，如何求出带惩罚因子的目标函数的最大值，细节还是比较多的：
+1.处理到i时，如何表示之前一个子数组都没选，i结尾的子数组是第一个子数组
+2.除了求出带惩罚因子的目标函数的最大值之外，还要求出得到这个最大值时，对应的m值是多少，如果有多个m值都能达到时，该取哪个
+-- 需要取最小的。但如果另一个更大的m值也能取到相同的最大值，会如何？如果这更大的m大于题目指定的m，那这个m不合法，如果这个m小于等于题目指定的m，也没关系，这时二分还没结束，还能通过调大惩罚因子，再求一次。可能得到恰好为m的一个值
+3.二分需要浮点数吗？--不需要，参考TsReaper的题解
+4.整数二分的结果可能并不会找到一个恰好为m的惩罚因子，此时直接用&lt;m的最大的惩罚因子即可</t>
+  </si>
+  <si>
+    <t>统计机器人组数</t>
+  </si>
+  <si>
+    <t>倒序遍历</t>
+  </si>
+  <si>
+    <t>先做一次合并处理，再倒序</t>
+  </si>
+  <si>
+    <t>至多 K 次转向的最小路径代价</t>
+  </si>
+  <si>
+    <t>统计好循环移位的数量</t>
+  </si>
+  <si>
+    <t>恰好有 K 对相等相邻字符的循环移位数量</t>
+  </si>
+  <si>
+    <t>得到恰好 N 分的最少天数</t>
+  </si>
+  <si>
+    <t>思维难度太大，知道之后，容易理解，代码也不复杂</t>
+  </si>
+  <si>
+    <t>凸函数</t>
+  </si>
+  <si>
+    <t>思维难度极大，看了题解还是很难理解，
+勉强理解后，代码写法上的技巧也很多，也很难理解
+https://www.cnblogs.com/wyzwyz/p/14038855.html
+这题花了好几周的时间</t>
+  </si>
+  <si>
+    <t>使每个元素变为回文数的最少操作次数</t>
+  </si>
+  <si>
+    <t>统计遥远子数组的数目</t>
+  </si>
+  <si>
+    <t>离散化树状数组</t>
+  </si>
+  <si>
+    <t>前缀和的树状数组</t>
+  </si>
+  <si>
+    <t>统计影子数对 I</t>
+  </si>
+  <si>
+    <t>单调栈 + DP</t>
+  </si>
+  <si>
+    <t>个人解法：得到一个性质，数对具有传递性 如果(nums[i],nums[j]) 和 (nums[j],nums[k]) 都是一对，那么  (nums[i],nums[k])也是一对</t>
+  </si>
+  <si>
+    <t>统计等间距出现整数数目 I</t>
+  </si>
+  <si>
+    <t>统计等间距出现整数数目 II</t>
+  </si>
+  <si>
+    <t>行列循环移位</t>
+  </si>
+  <si>
+    <t>LCP 60</t>
+  </si>
+  <si>
+    <t>力扣泡泡龙</t>
+  </si>
+  <si>
+    <t>思维难度很大，写法有点技巧，先将树转成数组形式，记录每行的前缀和</t>
+  </si>
+  <si>
+    <t>一个子数组循环移动后的最大脉冲值</t>
+  </si>
+  <si>
+    <t>统计相交区间对 II</t>
+  </si>
+  <si>
+    <t>开始容易往二分上考虑（看别人的题解，也有用二分的，没细看）
+重要结论：答案的上界是 2 * max(operate)，想清楚这个很关键
+更难的是，DP的状态设计，能想到这种状态的难度太大</t>
+  </si>
+  <si>
+    <t>考虑空闲时间的会议最大收益</t>
+  </si>
+  <si>
+    <t>式子变形 + 单调栈</t>
+  </si>
+  <si>
+    <t>统计相交区间对 I</t>
+  </si>
+  <si>
+    <t>同4057题</t>
+  </si>
+  <si>
+    <t>思维题 + 数据结构题</t>
+  </si>
+  <si>
+    <t>思维难度大，叠加树状数组和有序数组，代码也不少</t>
+  </si>
+  <si>
+    <t>至多一次取反能被 K 整除的最长子数组 I</t>
+  </si>
+  <si>
+    <t>C++要注意负数取模运算</t>
+  </si>
+  <si>
+    <t>至多一次替换后的最大相邻相等元素对数</t>
+  </si>
+  <si>
+    <t>不算难，但容易漏情况</t>
+  </si>
+  <si>
+    <t>数对和受限的最长子数组</t>
+  </si>
+  <si>
+    <t>个人解法，写法有点复杂</t>
+  </si>
+  <si>
+    <t>字典序最大的答案数组</t>
+  </si>
+  <si>
+    <t>稍有些技巧</t>
+  </si>
+  <si>
+    <t>成对操作转化数组</t>
+  </si>
+  <si>
+    <t>统计影子数对 II</t>
+  </si>
+  <si>
+    <t>值域分治</t>
+  </si>
+  <si>
+    <t>LCP 70</t>
+  </si>
+  <si>
+    <t>沙地治理</t>
+  </si>
+  <si>
+    <t>找规律，规律不容易发现</t>
+  </si>
+  <si>
+    <t>皇后到达目标格子的最少移动步数</t>
+  </si>
+  <si>
+    <t>只有两种情况</t>
+  </si>
+  <si>
+    <t>最小化最大可能等待时间</t>
+  </si>
+  <si>
+    <t>阅读理解，题意不是很明确</t>
+  </si>
+  <si>
+    <t>移除不同值重排数组</t>
+  </si>
+  <si>
+    <t>拨号的最少旋转次数 II</t>
+  </si>
+  <si>
+    <t>枚举分割点</t>
+  </si>
+  <si>
+    <t>LCP 71</t>
+  </si>
+  <si>
+    <t>集水器</t>
+  </si>
+  <si>
+    <t>建图+并查集</t>
+  </si>
+  <si>
+    <t>建图，遍历都有技巧，属于告诉你思路不难理解，但不告诉你思路很难想到的类型
+写法上也有技巧</t>
+  </si>
+  <si>
+    <t>一次删除后的最大交替子数组和</t>
+  </si>
+  <si>
+    <t>前后缀分解 + 分类讨论</t>
+  </si>
+  <si>
+    <t>个人解法有点复杂了，
+其他解法：状态机DP，没有往那个方向考虑</t>
+  </si>
+  <si>
+    <t>LCP 75</t>
+  </si>
+  <si>
+    <t>传送卷轴</t>
+  </si>
+  <si>
+    <t>题意表述不是很清楚
+一种情况，如果守护者无法使用卷轴，则答案为0，这种情况，题目没有交代</t>
+  </si>
+  <si>
+    <t>两大难点：1. 对于给定的x,y如何判断对于某个k，是否能满足相邻元素差值不超过k，这需要一个DP
+2. 如何确定x,y的值，先算出和 −1 相邻的最小值 l 和最大值 r，以及非 −1 相邻最大差值作为二分最小值，(r−l)/2 作为二分最大值，对于某个目标值k，x=l+k,y=r−k，如果这对x,y不能满足，则其他x,y也不能满足，这点很关键</t>
+  </si>
+  <si>
+    <t>最长有韧性的子数组 II</t>
+  </si>
+  <si>
+    <t>简单数论</t>
+  </si>
+  <si>
+    <t>至多 K 次交换后最大子数组和</t>
+  </si>
+  <si>
+    <t>对顶堆的想法倒是比较容易理解，写起来也还好，只是这题有点卡常，需要很大的优化</t>
+  </si>
+  <si>
+    <t>84(3700题)</t>
+  </si>
+  <si>
+    <t>选择质数子集 I</t>
+  </si>
+  <si>
+    <t>质数筛 + 二分</t>
+  </si>
+  <si>
+    <t>设计公交车座位预订系统</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -23315,17 +23908,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -23982,12 +24575,54 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13373100" y="109539405"/>
+          <a:off x="13373100" y="109722285"/>
           <a:ext cx="5427980" cy="1866900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3607</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1367155</xdr:colOff>
+      <xdr:row>3607</xdr:row>
+      <xdr:rowOff>709295</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3" r:link="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13373100" y="853868625"/>
+          <a:ext cx="1367155" cy="709295"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -24282,7 +24917,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3585"/>
+  <dimension ref="A1:N3695"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -26520,7 +27155,7 @@
         <v>29043</v>
       </c>
     </row>
-    <row r="106" ht="72" spans="1:11">
+    <row r="106" ht="86.4" spans="1:11">
       <c r="A106">
         <v>678</v>
       </c>
@@ -98971,6 +99606,9 @@
       <c r="E3572" t="s">
         <v>101</v>
       </c>
+      <c r="F3572">
+        <v>1754</v>
+      </c>
       <c r="G3572" s="1" t="s">
         <v>1631</v>
       </c>
@@ -98991,6 +99629,9 @@
       <c r="E3573" t="s">
         <v>34</v>
       </c>
+      <c r="F3573">
+        <v>1328</v>
+      </c>
       <c r="G3573" s="1" t="s">
         <v>6313</v>
       </c>
@@ -99011,6 +99652,9 @@
       <c r="E3574" t="s">
         <v>101</v>
       </c>
+      <c r="F3574">
+        <v>1845</v>
+      </c>
       <c r="G3574" s="1" t="s">
         <v>6315</v>
       </c>
@@ -99034,6 +99678,9 @@
       <c r="E3575" t="s">
         <v>78</v>
       </c>
+      <c r="F3575">
+        <v>1180</v>
+      </c>
       <c r="G3575" s="1" t="s">
         <v>687</v>
       </c>
@@ -99099,12 +99746,36 @@
         <v>0.0094</v>
       </c>
     </row>
+    <row r="3578" spans="1:14">
+      <c r="A3578">
+        <v>3988</v>
+      </c>
+      <c r="B3578" t="s">
+        <v>6322</v>
+      </c>
+      <c r="C3578" s="2">
+        <v>46218</v>
+      </c>
+      <c r="D3578" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3578" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3578" s="1" t="s">
+        <v>6323</v>
+      </c>
+      <c r="N3578" s="17"/>
+    </row>
     <row r="3579" spans="1:14">
-      <c r="A3579">
-        <v>3454</v>
+      <c r="A3579" t="s">
+        <v>6324</v>
       </c>
       <c r="B3579" t="s">
-        <v>6322</v>
+        <v>6325</v>
+      </c>
+      <c r="C3579" s="2">
+        <v>46218</v>
       </c>
       <c r="D3579" t="s">
         <v>138</v>
@@ -99112,100 +99783,2575 @@
       <c r="E3579" t="s">
         <v>74</v>
       </c>
-      <c r="F3579">
-        <v>2671</v>
-      </c>
       <c r="G3579" s="1" t="s">
-        <v>929</v>
-      </c>
+        <v>6326</v>
+      </c>
+      <c r="H3579" s="1" t="s">
+        <v>6327</v>
+      </c>
+      <c r="N3579" s="17"/>
     </row>
     <row r="3580" spans="1:14">
       <c r="A3580">
-        <v>3562</v>
+        <v>3989</v>
       </c>
       <c r="B3580" t="s">
-        <v>6323</v>
+        <v>6328</v>
+      </c>
+      <c r="C3580" s="2">
+        <v>46218</v>
       </c>
       <c r="D3580" t="s">
         <v>138</v>
       </c>
-      <c r="F3580">
-        <v>2458</v>
-      </c>
+      <c r="E3580" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3580" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N3580" s="17"/>
     </row>
     <row r="3581" spans="1:14">
-      <c r="A3581" t="s">
-        <v>6274</v>
+      <c r="A3581">
+        <v>3986</v>
       </c>
       <c r="B3581" t="s">
-        <v>6275</v>
+        <v>6329</v>
+      </c>
+      <c r="C3581" s="2">
+        <v>46221</v>
       </c>
       <c r="D3581" t="s">
-        <v>138</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="E3581" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3581">
+        <v>1205</v>
+      </c>
+      <c r="G3581" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N3581" s="17"/>
     </row>
     <row r="3582" spans="1:14">
       <c r="A3582">
-        <v>3721</v>
+        <v>3987</v>
       </c>
       <c r="B3582" t="s">
-        <v>6324</v>
+        <v>6330</v>
+      </c>
+      <c r="C3582" s="2">
+        <v>46221</v>
       </c>
       <c r="D3582" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E3582" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="F3582">
-        <v>2723</v>
-      </c>
+        <v>1549</v>
+      </c>
+      <c r="G3582" s="1" t="s">
+        <v>6331</v>
+      </c>
+      <c r="H3582" s="1" t="s">
+        <v>6332</v>
+      </c>
+      <c r="N3582" s="17"/>
     </row>
     <row r="3583" spans="1:14">
       <c r="A3583">
-        <v>3235</v>
+        <v>3985</v>
       </c>
       <c r="B3583" t="s">
-        <v>6325</v>
-      </c>
-      <c r="C3583" s="2"/>
+        <v>6333</v>
+      </c>
+      <c r="C3583" s="2">
+        <v>46221</v>
+      </c>
       <c r="D3583" t="s">
         <v>138</v>
       </c>
+      <c r="E3583" t="s">
+        <v>74</v>
+      </c>
       <c r="F3583">
-        <v>3773</v>
-      </c>
+        <v>2201</v>
+      </c>
+      <c r="G3583" s="1" t="s">
+        <v>4638</v>
+      </c>
+      <c r="H3583" s="1" t="s">
+        <v>4639</v>
+      </c>
+      <c r="N3583" s="17"/>
     </row>
     <row r="3584" spans="1:14">
       <c r="A3584">
+        <v>3994</v>
+      </c>
+      <c r="B3584" t="s">
+        <v>6334</v>
+      </c>
+      <c r="C3584" s="2">
+        <v>46222</v>
+      </c>
+      <c r="D3584" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3584" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3584" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="H3584" s="1" t="s">
+        <v>6335</v>
+      </c>
+      <c r="N3584" s="17"/>
+    </row>
+    <row r="3585" spans="1:14">
+      <c r="A3585">
+        <v>3993</v>
+      </c>
+      <c r="B3585" t="s">
+        <v>6336</v>
+      </c>
+      <c r="C3585" s="2">
+        <v>46222</v>
+      </c>
+      <c r="D3585" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3585" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3585" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="N3585" s="17"/>
+    </row>
+    <row r="3586" spans="1:14">
+      <c r="A3586">
+        <v>3992</v>
+      </c>
+      <c r="B3586" t="s">
+        <v>6337</v>
+      </c>
+      <c r="C3586" s="2">
+        <v>46222</v>
+      </c>
+      <c r="D3586" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3586" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3586" s="1" t="s">
+        <v>5022</v>
+      </c>
+      <c r="N3586" s="17"/>
+    </row>
+    <row r="3587" spans="1:14">
+      <c r="A3587">
+        <v>3997</v>
+      </c>
+      <c r="B3587" t="s">
+        <v>6338</v>
+      </c>
+      <c r="C3587" s="2">
+        <v>46226</v>
+      </c>
+      <c r="D3587" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3587" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3587">
+        <v>1426</v>
+      </c>
+      <c r="G3587" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3587" s="17"/>
+    </row>
+    <row r="3588" spans="1:14">
+      <c r="A3588">
+        <v>3999</v>
+      </c>
+      <c r="B3588" t="s">
+        <v>6339</v>
+      </c>
+      <c r="C3588" s="2">
+        <v>46226</v>
+      </c>
+      <c r="D3588" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3588" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3588" s="1" t="s">
+        <v>6340</v>
+      </c>
+      <c r="H3588" s="1" t="s">
+        <v>6341</v>
+      </c>
+      <c r="N3588" s="17"/>
+    </row>
+    <row r="3589" spans="1:14">
+      <c r="A3589">
+        <v>3995</v>
+      </c>
+      <c r="B3589" t="s">
+        <v>6342</v>
+      </c>
+      <c r="C3589" s="2">
+        <v>46226</v>
+      </c>
+      <c r="D3589" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3589" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3589" s="1" t="s">
+        <v>6343</v>
+      </c>
+      <c r="N3589" s="17"/>
+    </row>
+    <row r="3590" spans="1:14">
+      <c r="A3590">
+        <v>3996</v>
+      </c>
+      <c r="B3590" t="s">
+        <v>6344</v>
+      </c>
+      <c r="C3590" s="2">
+        <v>46228</v>
+      </c>
+      <c r="D3590" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3590" t="s">
+        <v>226</v>
+      </c>
+      <c r="F3590">
+        <v>1260</v>
+      </c>
+      <c r="G3590" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3590" s="1" t="s">
+        <v>6345</v>
+      </c>
+      <c r="N3590" s="17"/>
+    </row>
+    <row r="3591" spans="1:14">
+      <c r="A3591">
+        <v>3910</v>
+      </c>
+      <c r="B3591" t="s">
+        <v>6346</v>
+      </c>
+      <c r="C3591" s="2">
+        <v>46228</v>
+      </c>
+      <c r="D3591" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3591" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3591">
+        <v>1859</v>
+      </c>
+      <c r="G3591" s="1" t="s">
+        <v>5024</v>
+      </c>
+      <c r="N3591" s="17"/>
+    </row>
+    <row r="3592" spans="1:14">
+      <c r="A3592">
+        <v>3998</v>
+      </c>
+      <c r="B3592" t="s">
+        <v>6347</v>
+      </c>
+      <c r="C3592" s="2">
+        <v>46233</v>
+      </c>
+      <c r="D3592" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3592" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3592">
+        <v>1862</v>
+      </c>
+      <c r="G3592" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="H3592" s="1" t="s">
+        <v>6348</v>
+      </c>
+      <c r="N3592" s="17"/>
+    </row>
+    <row r="3593" spans="1:14">
+      <c r="A3593">
+        <v>2408</v>
+      </c>
+      <c r="B3593" t="s">
+        <v>6349</v>
+      </c>
+      <c r="C3593" s="2">
+        <v>46233</v>
+      </c>
+      <c r="D3593" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3593" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3593" s="1" t="s">
+        <v>4095</v>
+      </c>
+      <c r="N3593" s="17"/>
+    </row>
+    <row r="3594" spans="1:14">
+      <c r="A3594">
+        <v>4001</v>
+      </c>
+      <c r="B3594" t="s">
+        <v>6350</v>
+      </c>
+      <c r="C3594" s="2">
+        <v>46233</v>
+      </c>
+      <c r="D3594" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3594" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3594">
+        <v>1506</v>
+      </c>
+      <c r="G3594" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="H3594" s="1" t="s">
+        <v>6351</v>
+      </c>
+      <c r="N3594" s="17"/>
+    </row>
+    <row r="3595" spans="1:14">
+      <c r="A3595">
+        <v>4002</v>
+      </c>
+      <c r="B3595" t="s">
+        <v>6352</v>
+      </c>
+      <c r="C3595" s="2">
+        <v>46235</v>
+      </c>
+      <c r="D3595" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3595" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3595">
+        <v>1912</v>
+      </c>
+      <c r="G3595" s="1" t="s">
+        <v>6353</v>
+      </c>
+      <c r="H3595" s="1" t="s">
+        <v>6354</v>
+      </c>
+      <c r="N3595" s="17"/>
+    </row>
+    <row r="3596" spans="1:14">
+      <c r="A3596">
+        <v>3901</v>
+      </c>
+      <c r="B3596" t="s">
+        <v>6355</v>
+      </c>
+      <c r="C3596" s="2">
+        <v>46235</v>
+      </c>
+      <c r="D3596" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3596" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3596">
+        <v>2544</v>
+      </c>
+      <c r="G3596" s="1" t="s">
+        <v>6356</v>
+      </c>
+      <c r="H3596" s="1" t="s">
+        <v>6357</v>
+      </c>
+      <c r="N3596" s="17"/>
+    </row>
+    <row r="3597" spans="1:14">
+      <c r="A3597">
+        <v>4003</v>
+      </c>
+      <c r="B3597" t="s">
+        <v>6358</v>
+      </c>
+      <c r="C3597" s="2">
+        <v>46235</v>
+      </c>
+      <c r="D3597" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3597" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3597">
+        <v>2122</v>
+      </c>
+      <c r="G3597" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="N3597" s="17"/>
+    </row>
+    <row r="3598" spans="1:14">
+      <c r="A3598">
+        <v>4000</v>
+      </c>
+      <c r="B3598" t="s">
+        <v>6359</v>
+      </c>
+      <c r="C3598" s="2">
+        <v>46236</v>
+      </c>
+      <c r="D3598" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3598" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3598">
+        <v>1199</v>
+      </c>
+      <c r="G3598" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="N3598" s="17"/>
+    </row>
+    <row r="3599" spans="1:14">
+      <c r="A3599">
+        <v>3911</v>
+      </c>
+      <c r="B3599" t="s">
+        <v>6360</v>
+      </c>
+      <c r="C3599" s="2">
+        <v>46236</v>
+      </c>
+      <c r="D3599" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3599" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3599">
+        <v>2155</v>
+      </c>
+      <c r="G3599" s="1" t="s">
+        <v>6361</v>
+      </c>
+      <c r="H3599" s="1" t="s">
+        <v>6362</v>
+      </c>
+      <c r="N3599" s="17"/>
+    </row>
+    <row r="3600" spans="1:14">
+      <c r="A3600">
+        <v>4008</v>
+      </c>
+      <c r="B3600" t="s">
+        <v>6363</v>
+      </c>
+      <c r="C3600" s="2">
+        <v>46236</v>
+      </c>
+      <c r="D3600" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3600" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3600" s="1" t="s">
+        <v>6364</v>
+      </c>
+      <c r="N3600" s="17"/>
+    </row>
+    <row r="3601" spans="1:14">
+      <c r="A3601">
+        <v>3928</v>
+      </c>
+      <c r="B3601" t="s">
+        <v>6365</v>
+      </c>
+      <c r="C3601" s="2">
+        <v>46238</v>
+      </c>
+      <c r="D3601" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3601" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3601">
+        <v>2186</v>
+      </c>
+      <c r="G3601" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="H3601" s="1" t="s">
+        <v>6366</v>
+      </c>
+      <c r="N3601" s="17"/>
+    </row>
+    <row r="3602" spans="1:14">
+      <c r="A3602">
+        <v>4012</v>
+      </c>
+      <c r="B3602" t="s">
+        <v>6367</v>
+      </c>
+      <c r="C3602" s="2">
+        <v>46238</v>
+      </c>
+      <c r="D3602" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3602" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3602" s="1" t="s">
+        <v>6368</v>
+      </c>
+      <c r="N3602" s="17"/>
+    </row>
+    <row r="3603" spans="1:14">
+      <c r="A3603">
+        <v>4007</v>
+      </c>
+      <c r="B3603" t="s">
+        <v>6369</v>
+      </c>
+      <c r="C3603" s="2">
+        <v>46238</v>
+      </c>
+      <c r="D3603" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3603" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3603" s="1" t="s">
+        <v>2079</v>
+      </c>
+      <c r="H3603" s="1" t="s">
+        <v>6370</v>
+      </c>
+      <c r="N3603" s="17"/>
+    </row>
+    <row r="3604" spans="1:14">
+      <c r="A3604">
+        <v>4006</v>
+      </c>
+      <c r="B3604" t="s">
+        <v>6371</v>
+      </c>
+      <c r="C3604" s="2">
+        <v>46238</v>
+      </c>
+      <c r="D3604" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3604" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3604" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N3604" s="17"/>
+    </row>
+    <row r="3605" spans="1:14">
+      <c r="A3605">
+        <v>4013</v>
+      </c>
+      <c r="B3605" t="s">
+        <v>6372</v>
+      </c>
+      <c r="C3605" s="2">
+        <v>46241</v>
+      </c>
+      <c r="D3605" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3605" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3605" s="1" t="s">
+        <v>6008</v>
+      </c>
+      <c r="H3605" s="1" t="s">
+        <v>6373</v>
+      </c>
+      <c r="N3605" s="17"/>
+    </row>
+    <row r="3606" spans="1:14">
+      <c r="A3606">
+        <v>4010</v>
+      </c>
+      <c r="B3606" t="s">
+        <v>6374</v>
+      </c>
+      <c r="C3606" s="2">
+        <v>46241</v>
+      </c>
+      <c r="D3606" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3606" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3606" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N3606" s="17"/>
+    </row>
+    <row r="3607" ht="28.8" spans="1:14">
+      <c r="A3607">
+        <v>3348</v>
+      </c>
+      <c r="B3607" t="s">
+        <v>6375</v>
+      </c>
+      <c r="C3607" s="2">
+        <v>46242</v>
+      </c>
+      <c r="D3607" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3607" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3607">
+        <v>3101</v>
+      </c>
+      <c r="G3607" s="1" t="s">
+        <v>6376</v>
+      </c>
+      <c r="H3607" s="1" t="s">
+        <v>6377</v>
+      </c>
+      <c r="N3607" s="17"/>
+    </row>
+    <row r="3608" ht="72" spans="1:14">
+      <c r="A3608" t="s">
+        <v>6378</v>
+      </c>
+      <c r="B3608" t="s">
+        <v>6379</v>
+      </c>
+      <c r="C3608" s="2">
+        <v>46243</v>
+      </c>
+      <c r="D3608" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3608" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3608" s="1" t="s">
+        <v>6380</v>
+      </c>
+      <c r="H3608" s="1" t="s">
+        <v>6381</v>
+      </c>
+      <c r="I3608"/>
+      <c r="N3608" s="17"/>
+    </row>
+    <row r="3609" spans="1:14">
+      <c r="A3609">
+        <v>4016</v>
+      </c>
+      <c r="B3609" t="s">
+        <v>6382</v>
+      </c>
+      <c r="C3609" s="2">
+        <v>46243</v>
+      </c>
+      <c r="D3609" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3609" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3609" s="1" t="s">
+        <v>6383</v>
+      </c>
+      <c r="H3609" s="1" t="s">
+        <v>6384</v>
+      </c>
+      <c r="N3609" s="17"/>
+    </row>
+    <row r="3610" spans="1:14">
+      <c r="A3610">
+        <v>4015</v>
+      </c>
+      <c r="B3610" t="s">
+        <v>6385</v>
+      </c>
+      <c r="C3610" s="2">
+        <v>46243</v>
+      </c>
+      <c r="D3610" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3610" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3610" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3610" s="17"/>
+    </row>
+    <row r="3611" spans="1:14">
+      <c r="A3611">
+        <v>3981</v>
+      </c>
+      <c r="B3611" t="s">
+        <v>6386</v>
+      </c>
+      <c r="C3611" s="2">
+        <v>46249</v>
+      </c>
+      <c r="D3611" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3611" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3611">
+        <v>2128</v>
+      </c>
+      <c r="G3611" s="1" t="s">
+        <v>6387</v>
+      </c>
+      <c r="H3611" s="1" t="s">
+        <v>6388</v>
+      </c>
+      <c r="N3611" s="17"/>
+    </row>
+    <row r="3612" spans="1:14">
+      <c r="A3612">
+        <v>2945</v>
+      </c>
+      <c r="B3612" t="s">
+        <v>2544</v>
+      </c>
+      <c r="C3612" s="2">
+        <v>46249</v>
+      </c>
+      <c r="D3612" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3612" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3612">
+        <v>2943</v>
+      </c>
+      <c r="G3612" s="1" t="s">
+        <v>6389</v>
+      </c>
+      <c r="H3612" s="1" t="s">
+        <v>6390</v>
+      </c>
+      <c r="N3612" s="17"/>
+    </row>
+    <row r="3613" spans="1:14">
+      <c r="A3613">
+        <v>4014</v>
+      </c>
+      <c r="B3613" t="s">
+        <v>6391</v>
+      </c>
+      <c r="C3613" s="2">
+        <v>46249</v>
+      </c>
+      <c r="D3613" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3613" t="s">
+        <v>226</v>
+      </c>
+      <c r="G3613" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="H3613" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N3613" s="17"/>
+    </row>
+    <row r="3614" ht="28.8" spans="1:14">
+      <c r="A3614">
+        <v>4017</v>
+      </c>
+      <c r="B3614" t="s">
+        <v>6392</v>
+      </c>
+      <c r="C3614" s="2">
+        <v>46250</v>
+      </c>
+      <c r="D3614" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3614" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3614" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="H3614" s="1" t="s">
+        <v>6393</v>
+      </c>
+      <c r="N3614" s="17"/>
+    </row>
+    <row r="3615" spans="1:14">
+      <c r="A3615">
+        <v>4022</v>
+      </c>
+      <c r="B3615" t="s">
+        <v>6394</v>
+      </c>
+      <c r="C3615" s="2">
+        <v>46250</v>
+      </c>
+      <c r="D3615" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3615" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3615" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H3615" s="1" t="s">
+        <v>6395</v>
+      </c>
+      <c r="N3615" s="17"/>
+    </row>
+    <row r="3616" spans="1:14">
+      <c r="A3616">
+        <v>4026</v>
+      </c>
+      <c r="B3616" t="s">
+        <v>6396</v>
+      </c>
+      <c r="C3616" s="2">
+        <v>46250</v>
+      </c>
+      <c r="D3616" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3616" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3616" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="N3616" s="17"/>
+    </row>
+    <row r="3617" spans="1:14">
+      <c r="A3617">
+        <v>4027</v>
+      </c>
+      <c r="B3617" t="s">
+        <v>6397</v>
+      </c>
+      <c r="C3617" s="2">
+        <v>46253</v>
+      </c>
+      <c r="D3617" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3617" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3617">
+        <v>2200</v>
+      </c>
+      <c r="G3617" s="1" t="s">
+        <v>5760</v>
+      </c>
+      <c r="H3617" s="1" t="s">
+        <v>6398</v>
+      </c>
+      <c r="N3617" s="17"/>
+    </row>
+    <row r="3618" spans="1:14">
+      <c r="A3618">
+        <v>4021</v>
+      </c>
+      <c r="B3618" t="s">
+        <v>6399</v>
+      </c>
+      <c r="C3618" s="2">
+        <v>46253</v>
+      </c>
+      <c r="D3618" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3618" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3618" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="N3618" s="17"/>
+    </row>
+    <row r="3619" spans="1:14">
+      <c r="A3619">
+        <v>4025</v>
+      </c>
+      <c r="B3619" t="s">
+        <v>6400</v>
+      </c>
+      <c r="C3619" s="2">
+        <v>46253</v>
+      </c>
+      <c r="D3619" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3619" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3619" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="N3619" s="17"/>
+    </row>
+    <row r="3620" spans="1:14">
+      <c r="A3620">
+        <v>4023</v>
+      </c>
+      <c r="B3620" t="s">
+        <v>6401</v>
+      </c>
+      <c r="C3620" s="2">
+        <v>46255</v>
+      </c>
+      <c r="D3620" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3620" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3620">
+        <v>2279</v>
+      </c>
+      <c r="G3620" s="1" t="s">
+        <v>1772</v>
+      </c>
+      <c r="H3620" s="1" t="s">
+        <v>6402</v>
+      </c>
+      <c r="N3620" s="17"/>
+    </row>
+    <row r="3621" spans="1:14">
+      <c r="A3621">
+        <v>4011</v>
+      </c>
+      <c r="B3621" t="s">
+        <v>6403</v>
+      </c>
+      <c r="C3621" s="2">
+        <v>46255</v>
+      </c>
+      <c r="D3621" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3621" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3621">
+        <v>1391</v>
+      </c>
+      <c r="H3621" s="1" t="s">
+        <v>6404</v>
+      </c>
+      <c r="N3621" s="17"/>
+    </row>
+    <row r="3622" spans="1:14">
+      <c r="A3622">
+        <v>4024</v>
+      </c>
+      <c r="B3622" t="s">
+        <v>6405</v>
+      </c>
+      <c r="C3622" s="2">
+        <v>46255</v>
+      </c>
+      <c r="D3622" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3622" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3622" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N3622" s="17"/>
+    </row>
+    <row r="3623" spans="1:14">
+      <c r="A3623">
+        <v>3953</v>
+      </c>
+      <c r="B3623" t="s">
+        <v>6406</v>
+      </c>
+      <c r="C3623" s="2">
+        <v>46257</v>
+      </c>
+      <c r="D3623" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3623" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3623">
+        <v>2390</v>
+      </c>
+      <c r="G3623" s="1" t="s">
+        <v>6407</v>
+      </c>
+      <c r="H3623" s="1" t="s">
+        <v>6408</v>
+      </c>
+      <c r="N3623" s="17"/>
+    </row>
+    <row r="3624" spans="1:14">
+      <c r="A3624">
+        <v>4032</v>
+      </c>
+      <c r="B3624" t="s">
+        <v>6409</v>
+      </c>
+      <c r="C3624" s="2">
+        <v>46257</v>
+      </c>
+      <c r="D3624" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3624" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3624" s="1" t="s">
+        <v>6410</v>
+      </c>
+      <c r="N3624" s="17"/>
+    </row>
+    <row r="3625" spans="1:14">
+      <c r="A3625">
+        <v>4031</v>
+      </c>
+      <c r="B3625" t="s">
+        <v>6411</v>
+      </c>
+      <c r="C3625" s="2">
+        <v>46257</v>
+      </c>
+      <c r="D3625" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3625" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3625" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N3625" s="17"/>
+    </row>
+    <row r="3626" spans="1:14">
+      <c r="A3626">
+        <v>4033</v>
+      </c>
+      <c r="B3626" t="s">
+        <v>6412</v>
+      </c>
+      <c r="C3626" s="2">
+        <v>46262</v>
+      </c>
+      <c r="D3626" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3626" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3626" s="1" t="s">
+        <v>6413</v>
+      </c>
+      <c r="H3626" s="1" t="s">
+        <v>6414</v>
+      </c>
+      <c r="N3626" s="17"/>
+    </row>
+    <row r="3627" spans="1:14">
+      <c r="A3627">
+        <v>4020</v>
+      </c>
+      <c r="B3627" t="s">
+        <v>6415</v>
+      </c>
+      <c r="C3627" s="2">
+        <v>46262</v>
+      </c>
+      <c r="D3627" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3627" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3627">
+        <v>1187</v>
+      </c>
+      <c r="G3627" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N3627" s="17"/>
+    </row>
+    <row r="3628" spans="1:14">
+      <c r="A3628">
+        <v>4030</v>
+      </c>
+      <c r="B3628" t="s">
+        <v>6416</v>
+      </c>
+      <c r="C3628" s="2">
+        <v>46262</v>
+      </c>
+      <c r="D3628" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3628" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3628" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N3628" s="17"/>
+    </row>
+    <row r="3629" spans="1:14">
+      <c r="A3629">
+        <v>3956</v>
+      </c>
+      <c r="B3629" t="s">
+        <v>6417</v>
+      </c>
+      <c r="C3629" s="2">
+        <v>46264</v>
+      </c>
+      <c r="D3629" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3629" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3629" s="1" t="s">
+        <v>6418</v>
+      </c>
+      <c r="N3629" s="17"/>
+    </row>
+    <row r="3630" spans="1:14">
+      <c r="A3630">
+        <v>4036</v>
+      </c>
+      <c r="B3630" t="s">
+        <v>6419</v>
+      </c>
+      <c r="C3630" s="2">
+        <v>46264</v>
+      </c>
+      <c r="D3630" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3630" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3630" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N3630" s="17"/>
+    </row>
+    <row r="3631" spans="1:14">
+      <c r="A3631">
+        <v>4041</v>
+      </c>
+      <c r="B3631" t="s">
+        <v>6420</v>
+      </c>
+      <c r="C3631" s="2">
+        <v>46264</v>
+      </c>
+      <c r="D3631" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3631" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3631" s="1" t="s">
+        <v>3387</v>
+      </c>
+      <c r="N3631" s="17"/>
+    </row>
+    <row r="3632" spans="1:14">
+      <c r="A3632">
+        <v>4040</v>
+      </c>
+      <c r="B3632" t="s">
+        <v>6421</v>
+      </c>
+      <c r="C3632" s="2">
+        <v>46265</v>
+      </c>
+      <c r="D3632" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3632" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3632" s="1" t="s">
+        <v>4784</v>
+      </c>
+      <c r="H3632" s="1" t="s">
+        <v>6422</v>
+      </c>
+      <c r="N3632" s="17"/>
+    </row>
+    <row r="3633" spans="1:14">
+      <c r="A3633">
+        <v>4039</v>
+      </c>
+      <c r="B3633" t="s">
+        <v>6423</v>
+      </c>
+      <c r="C3633" s="2">
+        <v>46265</v>
+      </c>
+      <c r="D3633" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3633" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3633" s="1" t="s">
+        <v>2928</v>
+      </c>
+      <c r="N3633" s="17"/>
+    </row>
+    <row r="3634" ht="28.8" spans="1:14">
+      <c r="A3634">
+        <v>4034</v>
+      </c>
+      <c r="B3634" t="s">
+        <v>6424</v>
+      </c>
+      <c r="C3634" s="2">
+        <v>46265</v>
+      </c>
+      <c r="D3634" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3634" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3634" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H3634" s="1" t="s">
+        <v>6425</v>
+      </c>
+      <c r="N3634" s="17"/>
+    </row>
+    <row r="3635" spans="1:14">
+      <c r="A3635">
+        <v>4037</v>
+      </c>
+      <c r="B3635" t="s">
+        <v>6426</v>
+      </c>
+      <c r="C3635" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D3635" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3635" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3635" s="1" t="s">
+        <v>6427</v>
+      </c>
+      <c r="H3635" s="1" t="s">
+        <v>6428</v>
+      </c>
+      <c r="N3635" s="17"/>
+    </row>
+    <row r="3636" spans="1:14">
+      <c r="A3636">
+        <v>4036</v>
+      </c>
+      <c r="B3636" t="s">
+        <v>6429</v>
+      </c>
+      <c r="C3636" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D3636" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3636" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3636" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="H3636" s="1" t="s">
+        <v>6430</v>
+      </c>
+      <c r="N3636" s="17"/>
+    </row>
+    <row r="3637" spans="1:14">
+      <c r="A3637">
+        <v>4038</v>
+      </c>
+      <c r="B3637" t="s">
+        <v>6431</v>
+      </c>
+      <c r="C3637" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D3637" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3637" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3637" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="N3637" s="17"/>
+    </row>
+    <row r="3638" spans="1:14">
+      <c r="A3638">
+        <v>4039</v>
+      </c>
+      <c r="B3638" t="s">
+        <v>2910</v>
+      </c>
+      <c r="C3638" s="2">
+        <v>46272</v>
+      </c>
+      <c r="D3638" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3638" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3638">
+        <v>3111</v>
+      </c>
+      <c r="G3638" s="1" t="s">
+        <v>6432</v>
+      </c>
+      <c r="H3638" s="1" t="s">
+        <v>6433</v>
+      </c>
+      <c r="N3638" s="17"/>
+    </row>
+    <row r="3639" spans="1:14">
+      <c r="A3639" t="s">
+        <v>6434</v>
+      </c>
+      <c r="B3639" t="s">
+        <v>6435</v>
+      </c>
+      <c r="C3639" s="2"/>
+      <c r="D3639" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3639" t="s">
+        <v>74</v>
+      </c>
+      <c r="N3639" s="17"/>
+    </row>
+    <row r="3640" ht="158.4" spans="1:14">
+      <c r="A3640">
+        <v>3957</v>
+      </c>
+      <c r="B3640" t="s">
+        <v>6436</v>
+      </c>
+      <c r="C3640" s="2">
+        <v>46272</v>
+      </c>
+      <c r="D3640" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3640" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3640">
+        <v>2611</v>
+      </c>
+      <c r="G3640" s="1" t="s">
+        <v>6437</v>
+      </c>
+      <c r="H3640" s="1" t="s">
+        <v>6438</v>
+      </c>
+      <c r="N3640" s="17"/>
+    </row>
+    <row r="3641" spans="1:14">
+      <c r="A3641">
+        <v>4045</v>
+      </c>
+      <c r="B3641" t="s">
+        <v>6439</v>
+      </c>
+      <c r="C3641" s="2">
+        <v>46272</v>
+      </c>
+      <c r="D3641" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3641" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3641">
+        <v>1888</v>
+      </c>
+      <c r="G3641" s="1" t="s">
+        <v>6440</v>
+      </c>
+      <c r="H3641" s="1" t="s">
+        <v>6441</v>
+      </c>
+      <c r="N3641" s="17"/>
+    </row>
+    <row r="3642" spans="1:14">
+      <c r="A3642">
+        <v>4046</v>
+      </c>
+      <c r="B3642" t="s">
+        <v>6442</v>
+      </c>
+      <c r="C3642" s="2">
+        <v>46277</v>
+      </c>
+      <c r="D3642" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3642" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3642">
+        <v>2044</v>
+      </c>
+      <c r="G3642" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3642" s="17"/>
+    </row>
+    <row r="3643" spans="1:14">
+      <c r="A3643">
+        <v>4044</v>
+      </c>
+      <c r="B3643" t="s">
+        <v>6443</v>
+      </c>
+      <c r="C3643" s="2">
+        <v>46277</v>
+      </c>
+      <c r="D3643" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3643" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3643">
+        <v>1417</v>
+      </c>
+      <c r="G3643" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N3643" s="17"/>
+    </row>
+    <row r="3644" spans="1:14">
+      <c r="A3644">
+        <v>4043</v>
+      </c>
+      <c r="B3644" t="s">
+        <v>6444</v>
+      </c>
+      <c r="C3644" s="2">
+        <v>46277</v>
+      </c>
+      <c r="D3644" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3644" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3644">
+        <v>1209</v>
+      </c>
+      <c r="G3644" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3644" s="17"/>
+    </row>
+    <row r="3645" spans="1:14">
+      <c r="A3645">
+        <v>4050</v>
+      </c>
+      <c r="B3645" t="s">
+        <v>6445</v>
+      </c>
+      <c r="C3645" s="2">
+        <v>46278</v>
+      </c>
+      <c r="D3645" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3645" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3645">
+        <v>1696</v>
+      </c>
+      <c r="G3645" s="1" t="s">
+        <v>2480</v>
+      </c>
+      <c r="N3645" s="17"/>
+    </row>
+    <row r="3646" spans="1:14">
+      <c r="A3646">
+        <v>3389</v>
+      </c>
+      <c r="B3646" t="s">
+        <v>3965</v>
+      </c>
+      <c r="C3646" s="2">
+        <v>46278</v>
+      </c>
+      <c r="D3646" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3646" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3646">
+        <v>2940</v>
+      </c>
+      <c r="G3646" s="1" t="s">
+        <v>2162</v>
+      </c>
+      <c r="H3646" s="1" t="s">
+        <v>6446</v>
+      </c>
+      <c r="N3646" s="17"/>
+    </row>
+    <row r="3647" ht="57.6" spans="1:14">
+      <c r="A3647" t="s">
+        <v>6434</v>
+      </c>
+      <c r="B3647" t="s">
+        <v>6435</v>
+      </c>
+      <c r="C3647" s="2">
+        <v>46278</v>
+      </c>
+      <c r="D3647" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3647" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3647" s="1" t="s">
+        <v>6447</v>
+      </c>
+      <c r="H3647" s="1" t="s">
+        <v>6448</v>
+      </c>
+      <c r="N3647" s="17"/>
+    </row>
+    <row r="3648" spans="1:14">
+      <c r="A3648">
+        <v>4053</v>
+      </c>
+      <c r="B3648" t="s">
+        <v>6449</v>
+      </c>
+      <c r="C3648" s="2">
+        <v>46282</v>
+      </c>
+      <c r="D3648" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3648" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3648">
+        <v>2113</v>
+      </c>
+      <c r="G3648" s="1" t="s">
+        <v>6029</v>
+      </c>
+      <c r="H3648" s="1" t="s">
+        <v>6110</v>
+      </c>
+      <c r="N3648" s="17"/>
+    </row>
+    <row r="3649" spans="1:14">
+      <c r="A3649">
+        <v>4051</v>
+      </c>
+      <c r="B3649" t="s">
+        <v>6450</v>
+      </c>
+      <c r="C3649" s="2">
+        <v>46282</v>
+      </c>
+      <c r="D3649" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3649" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3649">
+        <v>2139</v>
+      </c>
+      <c r="G3649" s="1" t="s">
+        <v>6451</v>
+      </c>
+      <c r="H3649" s="1" t="s">
+        <v>6452</v>
+      </c>
+      <c r="N3649" s="17"/>
+    </row>
+    <row r="3650" ht="28.8" spans="1:14">
+      <c r="A3650">
+        <v>4054</v>
+      </c>
+      <c r="B3650" t="s">
+        <v>6453</v>
+      </c>
+      <c r="C3650" s="2">
+        <v>46282</v>
+      </c>
+      <c r="D3650" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3650" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3650">
+        <v>1820</v>
+      </c>
+      <c r="G3650" s="1" t="s">
+        <v>6454</v>
+      </c>
+      <c r="H3650" s="1" t="s">
+        <v>6455</v>
+      </c>
+      <c r="N3650" s="17"/>
+    </row>
+    <row r="3651" spans="1:14">
+      <c r="A3651">
+        <v>4048</v>
+      </c>
+      <c r="B3651" t="s">
+        <v>6456</v>
+      </c>
+      <c r="C3651" s="2">
+        <v>46284</v>
+      </c>
+      <c r="D3651" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3651" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3651">
+        <v>1191</v>
+      </c>
+      <c r="G3651" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="N3651" s="17"/>
+    </row>
+    <row r="3652" spans="1:14">
+      <c r="A3652">
+        <v>4049</v>
+      </c>
+      <c r="B3652" t="s">
+        <v>6457</v>
+      </c>
+      <c r="C3652" s="2">
+        <v>46284</v>
+      </c>
+      <c r="D3652" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3652" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3652">
+        <v>1405</v>
+      </c>
+      <c r="G3652" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="N3652" s="17"/>
+    </row>
+    <row r="3653" spans="1:14">
+      <c r="A3653">
+        <v>4052</v>
+      </c>
+      <c r="B3653" t="s">
+        <v>6458</v>
+      </c>
+      <c r="C3653" s="2">
+        <v>46284</v>
+      </c>
+      <c r="D3653" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3653" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3653">
+        <v>1246</v>
+      </c>
+      <c r="G3653" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N3653" s="17"/>
+    </row>
+    <row r="3654" spans="1:14">
+      <c r="A3654" t="s">
+        <v>6459</v>
+      </c>
+      <c r="B3654" t="s">
+        <v>6460</v>
+      </c>
+      <c r="C3654" s="2">
+        <v>46287</v>
+      </c>
+      <c r="D3654" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3654" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3654" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="H3654" s="1" t="s">
+        <v>6461</v>
+      </c>
+      <c r="N3654" s="17"/>
+    </row>
+    <row r="3655" spans="1:14">
+      <c r="A3655">
+        <v>4058</v>
+      </c>
+      <c r="B3655" t="s">
+        <v>6462</v>
+      </c>
+      <c r="C3655" s="2">
+        <v>46287</v>
+      </c>
+      <c r="D3655" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3655" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3655">
+        <v>1899</v>
+      </c>
+      <c r="G3655" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N3655" s="17"/>
+    </row>
+    <row r="3656" spans="1:14">
+      <c r="A3656">
+        <v>4057</v>
+      </c>
+      <c r="B3656" t="s">
+        <v>6463</v>
+      </c>
+      <c r="C3656" s="2">
+        <v>46287</v>
+      </c>
+      <c r="D3656" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3656" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3656">
+        <v>1483</v>
+      </c>
+      <c r="G3656" s="1" t="s">
+        <v>6301</v>
+      </c>
+      <c r="N3656" s="17"/>
+    </row>
+    <row r="3657" ht="43.2" spans="1:14">
+      <c r="A3657" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B3657" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C3657" s="2">
+        <v>46292</v>
+      </c>
+      <c r="D3657" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3657" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3657" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3657" s="1" t="s">
+        <v>6464</v>
+      </c>
+      <c r="N3657" s="17"/>
+    </row>
+    <row r="3658" spans="1:14">
+      <c r="A3658">
+        <v>4068</v>
+      </c>
+      <c r="B3658" t="s">
+        <v>6465</v>
+      </c>
+      <c r="C3658" s="2">
+        <v>46292</v>
+      </c>
+      <c r="D3658" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3658" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3658">
+        <v>2189</v>
+      </c>
+      <c r="G3658" s="1" t="s">
+        <v>6466</v>
+      </c>
+      <c r="N3658" s="17"/>
+    </row>
+    <row r="3659" spans="1:14">
+      <c r="A3659">
+        <v>4056</v>
+      </c>
+      <c r="B3659" t="s">
+        <v>6467</v>
+      </c>
+      <c r="C3659" s="2">
+        <v>46292</v>
+      </c>
+      <c r="D3659" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3659" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3659" s="1" t="s">
+        <v>6468</v>
+      </c>
+      <c r="N3659" s="17"/>
+    </row>
+    <row r="3660" spans="1:14">
+      <c r="A3660">
+        <v>3245</v>
+      </c>
+      <c r="B3660" t="s">
+        <v>3560</v>
+      </c>
+      <c r="C3660" s="2">
+        <v>46293</v>
+      </c>
+      <c r="D3660" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3660" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3660">
+        <v>3112</v>
+      </c>
+      <c r="G3660" s="1" t="s">
+        <v>6469</v>
+      </c>
+      <c r="H3660" s="1" t="s">
+        <v>6470</v>
+      </c>
+      <c r="N3660" s="17"/>
+    </row>
+    <row r="3661" spans="1:14">
+      <c r="A3661">
+        <v>4063</v>
+      </c>
+      <c r="B3661" t="s">
+        <v>6471</v>
+      </c>
+      <c r="C3661" s="2">
+        <v>46293</v>
+      </c>
+      <c r="D3661" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3661" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3661" s="1" t="s">
+        <v>6472</v>
+      </c>
+      <c r="N3661" s="17"/>
+    </row>
+    <row r="3662" spans="1:14">
+      <c r="A3662">
+        <v>4066</v>
+      </c>
+      <c r="B3662" t="s">
+        <v>6473</v>
+      </c>
+      <c r="C3662" s="2">
+        <v>46293</v>
+      </c>
+      <c r="D3662" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3662" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3662">
+        <v>1570</v>
+      </c>
+      <c r="G3662" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="H3662" s="1" t="s">
+        <v>6474</v>
+      </c>
+      <c r="N3662" s="17"/>
+    </row>
+    <row r="3663" spans="1:14">
+      <c r="A3663">
+        <v>4067</v>
+      </c>
+      <c r="B3663" t="s">
+        <v>6475</v>
+      </c>
+      <c r="C3663" s="2">
+        <v>46295</v>
+      </c>
+      <c r="D3663" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3663" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3663">
+        <v>1917</v>
+      </c>
+      <c r="G3663" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3663" s="1" t="s">
+        <v>6476</v>
+      </c>
+      <c r="N3663" s="17"/>
+    </row>
+    <row r="3664" spans="1:14">
+      <c r="A3664">
+        <v>4059</v>
+      </c>
+      <c r="B3664" t="s">
+        <v>6477</v>
+      </c>
+      <c r="C3664" s="2">
+        <v>46295</v>
+      </c>
+      <c r="D3664" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3664" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3664">
+        <v>2321</v>
+      </c>
+      <c r="G3664" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="H3664" s="1" t="s">
+        <v>6478</v>
+      </c>
+      <c r="N3664" s="17"/>
+    </row>
+    <row r="3665" spans="1:14">
+      <c r="A3665">
+        <v>4062</v>
+      </c>
+      <c r="B3665" t="s">
+        <v>6479</v>
+      </c>
+      <c r="C3665" s="2">
+        <v>46295</v>
+      </c>
+      <c r="D3665" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3665" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3665" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="N3665" s="17"/>
+    </row>
+    <row r="3666" spans="1:14">
+      <c r="A3666">
+        <v>4055</v>
+      </c>
+      <c r="B3666" t="s">
+        <v>6480</v>
+      </c>
+      <c r="C3666" s="2">
+        <v>46297</v>
+      </c>
+      <c r="D3666" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3666" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3666">
+        <v>2630</v>
+      </c>
+      <c r="G3666" s="1" t="s">
+        <v>6481</v>
+      </c>
+      <c r="N3666" s="17"/>
+    </row>
+    <row r="3667" spans="1:14">
+      <c r="A3667" t="s">
+        <v>6482</v>
+      </c>
+      <c r="B3667" t="s">
+        <v>6483</v>
+      </c>
+      <c r="C3667" s="2">
+        <v>46297</v>
+      </c>
+      <c r="D3667" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3667" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3667" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="H3667" s="1" t="s">
+        <v>6484</v>
+      </c>
+      <c r="N3667" s="17"/>
+    </row>
+    <row r="3668" spans="1:14">
+      <c r="A3668">
+        <v>4061</v>
+      </c>
+      <c r="B3668" t="s">
+        <v>6485</v>
+      </c>
+      <c r="C3668" s="2">
+        <v>46297</v>
+      </c>
+      <c r="D3668" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3668" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3668">
+        <v>1206</v>
+      </c>
+      <c r="H3668" s="1" t="s">
+        <v>6486</v>
+      </c>
+      <c r="N3668" s="17"/>
+    </row>
+    <row r="3669" spans="1:14">
+      <c r="A3669">
+        <v>4009</v>
+      </c>
+      <c r="B3669" t="s">
+        <v>6487</v>
+      </c>
+      <c r="C3669" s="2">
+        <v>46299</v>
+      </c>
+      <c r="D3669" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3669" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3669">
+        <v>2498</v>
+      </c>
+      <c r="G3669" s="1" t="s">
+        <v>3018</v>
+      </c>
+      <c r="H3669" s="1" t="s">
+        <v>6488</v>
+      </c>
+      <c r="N3669" s="17"/>
+    </row>
+    <row r="3670" spans="1:14">
+      <c r="A3670">
+        <v>4065</v>
+      </c>
+      <c r="B3670" t="s">
+        <v>6489</v>
+      </c>
+      <c r="C3670" s="2">
+        <v>46299</v>
+      </c>
+      <c r="D3670" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3670" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3670">
+        <v>1172</v>
+      </c>
+      <c r="G3670" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N3670" s="17"/>
+    </row>
+    <row r="3671" spans="1:14">
+      <c r="A3671">
+        <v>4071</v>
+      </c>
+      <c r="B3671" t="s">
+        <v>6490</v>
+      </c>
+      <c r="C3671" s="2">
+        <v>46299</v>
+      </c>
+      <c r="D3671" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3671" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3671" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="H3671" s="1" t="s">
+        <v>6491</v>
+      </c>
+    </row>
+    <row r="3672" ht="28.8" spans="1:14">
+      <c r="A3672" t="s">
+        <v>6492</v>
+      </c>
+      <c r="B3672" t="s">
+        <v>6493</v>
+      </c>
+      <c r="C3672" s="2">
+        <v>46300</v>
+      </c>
+      <c r="D3672" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3672" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3672" s="1" t="s">
+        <v>6494</v>
+      </c>
+      <c r="H3672" s="1" t="s">
+        <v>6495</v>
+      </c>
+      <c r="N3672" s="17"/>
+    </row>
+    <row r="3673" spans="1:14">
+      <c r="A3673">
+        <v>4070</v>
+      </c>
+      <c r="B3673" t="s">
+        <v>6490</v>
+      </c>
+      <c r="C3673" s="2">
+        <v>46300</v>
+      </c>
+      <c r="D3673" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3673" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3673" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N3673" s="17"/>
+    </row>
+    <row r="3674" ht="28.8" spans="1:14">
+      <c r="A3674">
+        <v>4072</v>
+      </c>
+      <c r="B3674" t="s">
+        <v>6496</v>
+      </c>
+      <c r="C3674" s="2">
+        <v>46300</v>
+      </c>
+      <c r="D3674" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3674" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3674" s="1" t="s">
+        <v>6497</v>
+      </c>
+      <c r="H3674" s="1" t="s">
+        <v>6498</v>
+      </c>
+      <c r="N3674" s="17"/>
+    </row>
+    <row r="3675" ht="28.8" spans="1:14">
+      <c r="A3675" t="s">
+        <v>6499</v>
+      </c>
+      <c r="B3675" t="s">
+        <v>6500</v>
+      </c>
+      <c r="C3675" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D3675" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3675" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="H3675" s="1" t="s">
+        <v>6501</v>
+      </c>
+      <c r="N3675" s="17"/>
+    </row>
+    <row r="3676" ht="72" spans="1:14">
+      <c r="A3676">
+        <v>3357</v>
+      </c>
+      <c r="B3676" t="s">
+        <v>3880</v>
+      </c>
+      <c r="C3676" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D3676" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3676" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3676">
+        <v>3077</v>
+      </c>
+      <c r="G3676" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H3676" s="1" t="s">
+        <v>6502</v>
+      </c>
+      <c r="N3676" s="17"/>
+    </row>
+    <row r="3677" spans="1:14">
+      <c r="A3677">
+        <v>4076</v>
+      </c>
+      <c r="B3677" t="s">
+        <v>6503</v>
+      </c>
+      <c r="C3677" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D3677" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3677" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3677" s="1" t="s">
+        <v>6504</v>
+      </c>
+      <c r="N3677" s="17"/>
+    </row>
+    <row r="3678" spans="1:14">
+      <c r="A3678">
+        <v>3962</v>
+      </c>
+      <c r="B3678" t="s">
+        <v>6505</v>
+      </c>
+      <c r="C3678" s="2">
+        <v>46310</v>
+      </c>
+      <c r="D3678" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3678" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3678">
+        <v>2672</v>
+      </c>
+      <c r="G3678" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="H3678" s="1" t="s">
+        <v>6506</v>
+      </c>
+      <c r="J3678" t="s">
+        <v>6507</v>
+      </c>
+      <c r="K3678">
+        <v>1507</v>
+      </c>
+      <c r="L3678">
+        <v>3661</v>
+      </c>
+      <c r="M3678">
+        <v>2341</v>
+      </c>
+      <c r="N3678" s="17">
+        <v>0.0096</v>
+      </c>
+    </row>
+    <row r="3679" spans="1:14">
+      <c r="A3679">
+        <v>4079</v>
+      </c>
+      <c r="B3679" t="s">
+        <v>6508</v>
+      </c>
+      <c r="C3679" s="2">
+        <v>46310</v>
+      </c>
+      <c r="D3679" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3679" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3679" s="1" t="s">
+        <v>6509</v>
+      </c>
+    </row>
+    <row r="3680" spans="1:14">
+      <c r="A3680">
+        <v>4080</v>
+      </c>
+      <c r="B3680" t="s">
+        <v>6510</v>
+      </c>
+      <c r="C3680" s="2">
+        <v>46310</v>
+      </c>
+      <c r="D3680" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3680" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3680" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="N3680" s="17"/>
+    </row>
+    <row r="3681" spans="1:14">
+      <c r="C3681" s="2"/>
+      <c r="N3681" s="17"/>
+    </row>
+    <row r="3682" spans="1:14">
+      <c r="C3682" s="2"/>
+      <c r="N3682" s="17"/>
+    </row>
+    <row r="3683" spans="1:14">
+      <c r="C3683" s="2"/>
+      <c r="N3683" s="17"/>
+    </row>
+    <row r="3684" spans="1:14">
+      <c r="C3684" s="2"/>
+      <c r="N3684" s="17"/>
+    </row>
+    <row r="3685" spans="1:14">
+      <c r="C3685" s="2"/>
+      <c r="N3685" s="17"/>
+    </row>
+    <row r="3686" spans="1:14">
+      <c r="C3686" s="2"/>
+      <c r="N3686" s="17"/>
+    </row>
+    <row r="3687" spans="1:14">
+      <c r="C3687" s="2"/>
+      <c r="N3687" s="17"/>
+    </row>
+    <row r="3689" spans="1:14">
+      <c r="A3689">
+        <v>3454</v>
+      </c>
+      <c r="B3689" t="s">
+        <v>6511</v>
+      </c>
+      <c r="D3689" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3689" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3689">
+        <v>2671</v>
+      </c>
+      <c r="G3689" s="1" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="3690" spans="1:14">
+      <c r="A3690">
+        <v>3562</v>
+      </c>
+      <c r="B3690" t="s">
+        <v>6512</v>
+      </c>
+      <c r="D3690" t="s">
+        <v>138</v>
+      </c>
+      <c r="F3690">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="3691" spans="1:14">
+      <c r="A3691" t="s">
+        <v>6274</v>
+      </c>
+      <c r="B3691" t="s">
+        <v>6275</v>
+      </c>
+      <c r="D3691" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3692" spans="1:14">
+      <c r="A3692">
+        <v>3721</v>
+      </c>
+      <c r="B3692" t="s">
+        <v>6513</v>
+      </c>
+      <c r="D3692" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3692" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3692">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="3693" spans="1:14">
+      <c r="A3693">
+        <v>3235</v>
+      </c>
+      <c r="B3693" t="s">
+        <v>6514</v>
+      </c>
+      <c r="C3693" s="2"/>
+      <c r="D3693" t="s">
+        <v>138</v>
+      </c>
+      <c r="F3693">
+        <v>3773</v>
+      </c>
+    </row>
+    <row r="3694" spans="1:14">
+      <c r="A3694">
         <v>3225</v>
       </c>
-      <c r="B3584" t="s">
-        <v>6326</v>
-      </c>
-      <c r="D3584" t="s">
+      <c r="B3694" t="s">
+        <v>6515</v>
+      </c>
+      <c r="D3694" t="s">
         <v>138</v>
       </c>
-      <c r="E3584" t="s">
+      <c r="E3694" t="s">
         <v>74</v>
       </c>
-      <c r="F3584">
+      <c r="F3694">
         <v>3028</v>
       </c>
     </row>
-    <row r="3585" spans="1:4">
-      <c r="A3585" t="s">
+    <row r="3695" spans="1:14">
+      <c r="A3695" t="s">
         <v>4851</v>
       </c>
-      <c r="B3585" t="s">
+      <c r="B3695" t="s">
         <v>4852</v>
       </c>
-      <c r="D3585" t="s">
+      <c r="D3695" t="s">
         <v>138</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3574" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3678" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -99253,10 +102399,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6327</v>
+        <v>6516</v>
       </c>
       <c r="D5" t="s">
-        <v>6328</v>
+        <v>6517</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -99267,13 +102413,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6329</v>
+        <v>6518</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6330</v>
+        <v>6519</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -99282,7 +102428,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6331</v>
+        <v>6520</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -99297,16 +102443,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6332</v>
+        <v>6521</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6333</v>
+        <v>6522</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6334</v>
+        <v>6523</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2964</v>
@@ -99320,10 +102466,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6335</v>
+        <v>6524</v>
       </c>
       <c r="H14" t="s">
-        <v>6336</v>
+        <v>6525</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -99338,16 +102484,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6337</v>
+        <v>6526</v>
       </c>
       <c r="W14" t="s">
-        <v>6338</v>
+        <v>6527</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6339</v>
+        <v>6528</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -99359,158 +102505,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6340</v>
+        <v>6529</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6341</v>
+        <v>6530</v>
       </c>
       <c r="AL14" t="s">
-        <v>6342</v>
+        <v>6531</v>
       </c>
       <c r="AO14" t="s">
-        <v>6343</v>
+        <v>6532</v>
       </c>
       <c r="AR14" t="s">
-        <v>6344</v>
+        <v>6533</v>
       </c>
       <c r="AU14" t="s">
-        <v>6345</v>
+        <v>6534</v>
       </c>
       <c r="AX14" t="s">
-        <v>6346</v>
+        <v>6535</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6347</v>
+        <v>6536</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6348</v>
+        <v>6537</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6349</v>
+        <v>6538</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6350</v>
+        <v>6539</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6351</v>
+        <v>6540</v>
       </c>
       <c r="T15" t="s">
-        <v>6352</v>
+        <v>6541</v>
       </c>
       <c r="W15" t="s">
-        <v>6353</v>
+        <v>6542</v>
       </c>
       <c r="Z15" t="s">
-        <v>6354</v>
+        <v>6543</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6355</v>
+        <v>6544</v>
       </c>
       <c r="AF15" t="s">
-        <v>6356</v>
+        <v>6545</v>
       </c>
       <c r="AI15" t="s">
-        <v>6357</v>
+        <v>6546</v>
       </c>
       <c r="AL15" t="s">
-        <v>6358</v>
+        <v>6547</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6359</v>
+        <v>6548</v>
       </c>
       <c r="AU15" t="s">
-        <v>6360</v>
+        <v>6549</v>
       </c>
       <c r="AX15" t="s">
-        <v>6361</v>
+        <v>6550</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6362</v>
+        <v>6551</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6363</v>
+        <v>6552</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6364</v>
+        <v>6553</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6365</v>
+        <v>6554</v>
       </c>
       <c r="H16" t="s">
-        <v>6366</v>
+        <v>6555</v>
       </c>
       <c r="N16" t="s">
-        <v>6367</v>
+        <v>6556</v>
       </c>
       <c r="T16" t="s">
-        <v>6368</v>
+        <v>6557</v>
       </c>
       <c r="W16" t="s">
-        <v>6369</v>
+        <v>6558</v>
       </c>
       <c r="Z16" t="s">
-        <v>6370</v>
+        <v>6559</v>
       </c>
       <c r="AC16" t="s">
-        <v>6358</v>
+        <v>6547</v>
       </c>
       <c r="AF16" t="s">
-        <v>6340</v>
+        <v>6529</v>
       </c>
       <c r="AI16" t="s">
-        <v>6371</v>
+        <v>6560</v>
       </c>
       <c r="AL16" t="s">
-        <v>6372</v>
+        <v>6561</v>
       </c>
       <c r="AR16" t="s">
-        <v>6373</v>
+        <v>6562</v>
       </c>
       <c r="AU16" t="s">
-        <v>6374</v>
+        <v>6563</v>
       </c>
       <c r="AX16" t="s">
-        <v>6375</v>
+        <v>6564</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6376</v>
+        <v>6565</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -99518,43 +102664,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6377</v>
+        <v>6566</v>
       </c>
       <c r="D17" t="s">
-        <v>6378</v>
+        <v>6567</v>
       </c>
       <c r="H17" t="s">
-        <v>6379</v>
+        <v>6568</v>
       </c>
       <c r="N17" t="s">
-        <v>6380</v>
+        <v>6569</v>
       </c>
       <c r="T17" t="s">
-        <v>6381</v>
+        <v>6570</v>
       </c>
       <c r="W17" t="s">
-        <v>6340</v>
+        <v>6529</v>
       </c>
       <c r="Z17" t="s">
-        <v>6351</v>
+        <v>6540</v>
       </c>
       <c r="AC17" t="s">
-        <v>6382</v>
+        <v>6571</v>
       </c>
       <c r="AF17" t="s">
-        <v>6383</v>
+        <v>6572</v>
       </c>
       <c r="AI17" t="s">
-        <v>6384</v>
+        <v>6573</v>
       </c>
       <c r="AR17" t="s">
-        <v>6385</v>
+        <v>6574</v>
       </c>
       <c r="AU17" t="s">
-        <v>6386</v>
+        <v>6575</v>
       </c>
       <c r="BA17" t="s">
-        <v>6387</v>
+        <v>6576</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -99562,37 +102708,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6388</v>
+        <v>6577</v>
       </c>
       <c r="H18" t="s">
-        <v>6389</v>
+        <v>6578</v>
       </c>
       <c r="N18" t="s">
-        <v>6390</v>
+        <v>6579</v>
       </c>
       <c r="T18" t="s">
-        <v>6391</v>
+        <v>6580</v>
       </c>
       <c r="W18" t="s">
-        <v>6392</v>
+        <v>6581</v>
       </c>
       <c r="Z18" t="s">
-        <v>6367</v>
+        <v>6556</v>
       </c>
       <c r="AC18" t="s">
-        <v>6393</v>
+        <v>6582</v>
       </c>
       <c r="AF18" t="s">
-        <v>6394</v>
+        <v>6583</v>
       </c>
       <c r="AI18" t="s">
-        <v>6395</v>
+        <v>6584</v>
       </c>
       <c r="AU18" t="s">
-        <v>6396</v>
+        <v>6585</v>
       </c>
       <c r="BA18" t="s">
-        <v>6397</v>
+        <v>6586</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -99600,37 +102746,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6398</v>
+        <v>6587</v>
       </c>
       <c r="H19" t="s">
-        <v>6399</v>
+        <v>6588</v>
       </c>
       <c r="N19" t="s">
-        <v>6400</v>
+        <v>6589</v>
       </c>
       <c r="T19" t="s">
-        <v>6401</v>
+        <v>6590</v>
       </c>
       <c r="W19" t="s">
-        <v>6375</v>
+        <v>6564</v>
       </c>
       <c r="Z19" t="s">
-        <v>6380</v>
+        <v>6569</v>
       </c>
       <c r="AC19" t="s">
-        <v>6402</v>
+        <v>6591</v>
       </c>
       <c r="AF19" t="s">
-        <v>6403</v>
+        <v>6592</v>
       </c>
       <c r="AI19" t="s">
-        <v>6404</v>
+        <v>6593</v>
       </c>
       <c r="AU19" t="s">
-        <v>6405</v>
+        <v>6594</v>
       </c>
       <c r="BA19" t="s">
-        <v>6406</v>
+        <v>6595</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -99638,37 +102784,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6407</v>
+        <v>6596</v>
       </c>
       <c r="D20" t="s">
-        <v>6408</v>
+        <v>6597</v>
       </c>
       <c r="H20" t="s">
-        <v>6409</v>
+        <v>6598</v>
       </c>
       <c r="N20" t="s">
-        <v>6410</v>
+        <v>6599</v>
       </c>
       <c r="T20" t="s">
-        <v>6411</v>
+        <v>6600</v>
       </c>
       <c r="W20" t="s">
-        <v>6403</v>
+        <v>6592</v>
       </c>
       <c r="Z20" t="s">
-        <v>6390</v>
+        <v>6579</v>
       </c>
       <c r="AC20" t="s">
-        <v>6412</v>
+        <v>6601</v>
       </c>
       <c r="AF20" t="s">
-        <v>6413</v>
+        <v>6602</v>
       </c>
       <c r="AU20" t="s">
-        <v>6414</v>
+        <v>6603</v>
       </c>
       <c r="BA20" t="s">
-        <v>6415</v>
+        <v>6604</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -99676,37 +102822,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6416</v>
+        <v>6605</v>
       </c>
       <c r="D21" t="s">
-        <v>6417</v>
+        <v>6606</v>
       </c>
       <c r="H21" t="s">
-        <v>6418</v>
+        <v>6607</v>
       </c>
       <c r="N21" t="s">
-        <v>6419</v>
+        <v>6608</v>
       </c>
       <c r="T21" t="s">
-        <v>6420</v>
+        <v>6609</v>
       </c>
       <c r="W21" t="s">
-        <v>6413</v>
+        <v>6602</v>
       </c>
       <c r="Z21" t="s">
-        <v>6400</v>
+        <v>6589</v>
       </c>
       <c r="AC21" t="s">
-        <v>6421</v>
+        <v>6610</v>
       </c>
       <c r="AF21" t="s">
-        <v>6422</v>
+        <v>6611</v>
       </c>
       <c r="AU21" t="s">
-        <v>6423</v>
+        <v>6612</v>
       </c>
       <c r="BA21" t="s">
-        <v>6424</v>
+        <v>6613</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -99717,13 +102863,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6425</v>
+        <v>6614</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6426</v>
+        <v>6615</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -99732,16 +102878,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6410</v>
+        <v>6599</v>
       </c>
       <c r="AC22" t="s">
-        <v>6427</v>
+        <v>6616</v>
       </c>
       <c r="AF22" t="s">
-        <v>6428</v>
+        <v>6617</v>
       </c>
       <c r="AU22" t="s">
-        <v>6429</v>
+        <v>6618</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -99749,25 +102895,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6430</v>
+        <v>6619</v>
       </c>
       <c r="H23" t="s">
-        <v>6431</v>
+        <v>6620</v>
       </c>
       <c r="T23" t="s">
-        <v>6432</v>
+        <v>6621</v>
       </c>
       <c r="Z23" t="s">
-        <v>6419</v>
+        <v>6608</v>
       </c>
       <c r="AC23" t="s">
-        <v>6433</v>
+        <v>6622</v>
       </c>
       <c r="AF23" t="s">
-        <v>6434</v>
+        <v>6623</v>
       </c>
       <c r="AU23" t="s">
-        <v>6435</v>
+        <v>6624</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -99775,89 +102921,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6436</v>
+        <v>6625</v>
       </c>
       <c r="T24" t="s">
-        <v>6437</v>
+        <v>6626</v>
       </c>
       <c r="Z24" t="s">
-        <v>6438</v>
+        <v>6627</v>
       </c>
       <c r="AC24" t="s">
-        <v>6439</v>
+        <v>6628</v>
       </c>
       <c r="AF24" t="s">
-        <v>6440</v>
+        <v>6629</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6441</v>
+        <v>6630</v>
       </c>
       <c r="D25" t="s">
-        <v>6442</v>
+        <v>6631</v>
       </c>
       <c r="T25" t="s">
-        <v>6443</v>
+        <v>6632</v>
       </c>
       <c r="AC25" t="s">
-        <v>6444</v>
+        <v>6633</v>
       </c>
       <c r="AF25" t="s">
-        <v>6445</v>
+        <v>6634</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6446</v>
+        <v>6635</v>
       </c>
       <c r="AC26" t="s">
-        <v>6447</v>
+        <v>6636</v>
       </c>
       <c r="AF26" t="s">
-        <v>6448</v>
+        <v>6637</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6449</v>
+        <v>6638</v>
       </c>
       <c r="AC27" t="s">
-        <v>6450</v>
+        <v>6639</v>
       </c>
       <c r="AF27" t="s">
-        <v>6451</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6452</v>
+        <v>6641</v>
       </c>
       <c r="AC28" t="s">
-        <v>6453</v>
+        <v>6642</v>
       </c>
       <c r="AF28" t="s">
-        <v>6454</v>
+        <v>6643</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6455</v>
+        <v>6644</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6456</v>
+        <v>6645</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6457</v>
+        <v>6646</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6458</v>
+        <v>6647</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -99867,22 +103013,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6459</v>
+        <v>6648</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6460</v>
+        <v>6649</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6461</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6462</v>
+        <v>6651</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -99892,7 +103038,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6463</v>
+        <v>6652</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -99900,7 +103046,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6464</v>
+        <v>6653</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -99915,7 +103061,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6465</v>
+        <v>6654</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -99933,227 +103079,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6466</v>
+        <v>6655</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6467</v>
+        <v>6656</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6468</v>
+        <v>6657</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6469</v>
+        <v>6658</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6470</v>
+        <v>6659</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6471</v>
+        <v>6660</v>
       </c>
       <c r="Q41" t="s">
-        <v>6459</v>
+        <v>6648</v>
       </c>
       <c r="T41" t="s">
-        <v>6355</v>
+        <v>6544</v>
       </c>
       <c r="W41" t="s">
-        <v>6472</v>
+        <v>6661</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6473</v>
+        <v>6662</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6474</v>
+        <v>6663</v>
       </c>
       <c r="AL41" t="s">
-        <v>6475</v>
+        <v>6664</v>
       </c>
       <c r="AO41" t="s">
-        <v>6476</v>
+        <v>6665</v>
       </c>
       <c r="AR41" t="s">
-        <v>6477</v>
+        <v>6666</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6478</v>
+        <v>6667</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6479</v>
+        <v>6668</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6480</v>
+        <v>6669</v>
       </c>
       <c r="Q42" t="s">
-        <v>6460</v>
+        <v>6649</v>
       </c>
       <c r="T42" t="s">
-        <v>6481</v>
+        <v>6670</v>
       </c>
       <c r="W42" t="s">
-        <v>6482</v>
+        <v>6671</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6483</v>
+        <v>6672</v>
       </c>
       <c r="AC42" t="s">
-        <v>6484</v>
+        <v>6673</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6485</v>
+        <v>6674</v>
       </c>
       <c r="AL42" t="s">
-        <v>6486</v>
+        <v>6675</v>
       </c>
       <c r="AO42" t="s">
-        <v>6487</v>
+        <v>6676</v>
       </c>
       <c r="AR42" t="s">
-        <v>6488</v>
+        <v>6677</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6489</v>
+        <v>6678</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6490</v>
+        <v>6679</v>
       </c>
       <c r="K43" t="s">
-        <v>6491</v>
+        <v>6680</v>
       </c>
       <c r="N43" t="s">
-        <v>6492</v>
+        <v>6681</v>
       </c>
       <c r="Q43" t="s">
-        <v>6461</v>
+        <v>6650</v>
       </c>
       <c r="T43" t="s">
-        <v>6493</v>
+        <v>6682</v>
       </c>
       <c r="W43" t="s">
-        <v>6494</v>
+        <v>6683</v>
       </c>
       <c r="Z43" t="s">
-        <v>6495</v>
+        <v>6684</v>
       </c>
       <c r="AC43" t="s">
-        <v>6496</v>
+        <v>6685</v>
       </c>
       <c r="AF43" t="s">
-        <v>6497</v>
+        <v>6686</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6498</v>
+        <v>6687</v>
       </c>
       <c r="AL43" t="s">
-        <v>6407</v>
+        <v>6596</v>
       </c>
       <c r="AO43" t="s">
-        <v>6499</v>
+        <v>6688</v>
       </c>
       <c r="AR43" t="s">
-        <v>6500</v>
+        <v>6689</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6501</v>
+        <v>6690</v>
       </c>
       <c r="F44" t="s">
-        <v>6502</v>
+        <v>6691</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6503</v>
+        <v>6692</v>
       </c>
       <c r="N44" t="s">
-        <v>6504</v>
+        <v>6693</v>
       </c>
       <c r="Q44" t="s">
-        <v>6462</v>
+        <v>6651</v>
       </c>
       <c r="W44" t="s">
-        <v>6505</v>
+        <v>6694</v>
       </c>
       <c r="Z44" t="s">
-        <v>6506</v>
+        <v>6695</v>
       </c>
       <c r="AC44" t="s">
-        <v>6507</v>
+        <v>6696</v>
       </c>
       <c r="AF44" t="s">
-        <v>6444</v>
+        <v>6633</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6508</v>
+        <v>6697</v>
       </c>
       <c r="AL44" t="s">
-        <v>6509</v>
+        <v>6698</v>
       </c>
       <c r="AO44" t="s">
-        <v>6510</v>
+        <v>6699</v>
       </c>
       <c r="AR44" t="s">
-        <v>6511</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6512</v>
+        <v>6701</v>
       </c>
       <c r="F45" t="s">
-        <v>6513</v>
+        <v>6702</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6514</v>
+        <v>6703</v>
       </c>
       <c r="N45" t="s">
-        <v>6515</v>
+        <v>6704</v>
       </c>
       <c r="Q45" t="s">
-        <v>6516</v>
+        <v>6705</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -100162,103 +103308,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6517</v>
+        <v>6706</v>
       </c>
       <c r="AF45" t="s">
-        <v>6518</v>
+        <v>6707</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6519</v>
+        <v>6708</v>
       </c>
       <c r="AO45" t="s">
-        <v>6520</v>
+        <v>6709</v>
       </c>
       <c r="AR45" t="s">
-        <v>6521</v>
+        <v>6710</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6522</v>
+        <v>6711</v>
       </c>
       <c r="F46" t="s">
-        <v>6523</v>
+        <v>6712</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6524</v>
+        <v>6713</v>
       </c>
       <c r="N46" t="s">
-        <v>6525</v>
+        <v>6714</v>
       </c>
       <c r="AC46" t="s">
-        <v>6526</v>
+        <v>6715</v>
       </c>
       <c r="AF46" t="s">
-        <v>6527</v>
+        <v>6716</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6528</v>
+        <v>6717</v>
       </c>
       <c r="AO46" t="s">
-        <v>6529</v>
+        <v>6718</v>
       </c>
       <c r="AR46" t="s">
-        <v>6530</v>
+        <v>6719</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6531</v>
+        <v>6720</v>
       </c>
       <c r="F47" t="s">
-        <v>6532</v>
+        <v>6721</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6533</v>
+        <v>6722</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6534</v>
+        <v>6723</v>
       </c>
       <c r="AC47" t="s">
-        <v>6535</v>
+        <v>6724</v>
       </c>
       <c r="AF47" t="s">
-        <v>6536</v>
+        <v>6725</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6537</v>
+        <v>6726</v>
       </c>
       <c r="AO47" t="s">
-        <v>6538</v>
+        <v>6727</v>
       </c>
       <c r="AR47" t="s">
-        <v>6539</v>
+        <v>6728</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6540</v>
+        <v>6729</v>
       </c>
       <c r="F48" t="s">
-        <v>6541</v>
+        <v>6730</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -100270,141 +103416,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6542</v>
+        <v>6731</v>
       </c>
       <c r="AF48" t="s">
-        <v>6543</v>
+        <v>6732</v>
       </c>
       <c r="AO48" t="s">
-        <v>6544</v>
+        <v>6733</v>
       </c>
       <c r="AR48" t="s">
-        <v>6545</v>
+        <v>6734</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6546</v>
+        <v>6735</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6547</v>
+        <v>6736</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6548</v>
+        <v>6737</v>
       </c>
       <c r="AF49" t="s">
-        <v>6549</v>
+        <v>6738</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6550</v>
+        <v>6739</v>
       </c>
       <c r="AR49" t="s">
-        <v>6551</v>
+        <v>6740</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6552</v>
+        <v>6741</v>
       </c>
       <c r="F50" t="s">
-        <v>6553</v>
+        <v>6742</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6554</v>
+        <v>6743</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6555</v>
+        <v>6744</v>
       </c>
       <c r="AR50" t="s">
-        <v>6556</v>
+        <v>6745</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6557</v>
+        <v>6746</v>
       </c>
       <c r="F51" t="s">
-        <v>6558</v>
+        <v>6747</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6559</v>
+        <v>6748</v>
       </c>
       <c r="AR51" t="s">
-        <v>6560</v>
+        <v>6749</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6561</v>
+        <v>6750</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6562</v>
+        <v>6751</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6563</v>
+        <v>6752</v>
       </c>
       <c r="AR52" t="s">
-        <v>6564</v>
+        <v>6753</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6565</v>
+        <v>6754</v>
       </c>
       <c r="F53" t="s">
-        <v>6566</v>
+        <v>6755</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6567</v>
+        <v>6756</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6568</v>
+        <v>6757</v>
       </c>
       <c r="F54" t="s">
-        <v>6569</v>
+        <v>6758</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6570</v>
+        <v>6759</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6571</v>
+        <v>6760</v>
       </c>
       <c r="F55" t="s">
-        <v>6572</v>
+        <v>6761</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -100412,10 +103558,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6573</v>
+        <v>6762</v>
       </c>
       <c r="F56" t="s">
-        <v>6574</v>
+        <v>6763</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -100423,18 +103569,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6575</v>
+        <v>6764</v>
       </c>
       <c r="F57" t="s">
-        <v>6576</v>
+        <v>6765</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6577</v>
+        <v>6766</v>
       </c>
       <c r="F58" t="s">
-        <v>6578</v>
+        <v>6767</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -100442,42 +103588,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6579</v>
+        <v>6768</v>
       </c>
       <c r="F59" t="s">
-        <v>6580</v>
+        <v>6769</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6581</v>
+        <v>6770</v>
       </c>
       <c r="F60" t="s">
-        <v>6582</v>
+        <v>6771</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6583</v>
+        <v>6772</v>
       </c>
       <c r="F61" t="s">
-        <v>6584</v>
+        <v>6773</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6585</v>
+        <v>6774</v>
       </c>
       <c r="F62" t="s">
-        <v>6586</v>
+        <v>6775</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6587</v>
+        <v>6776</v>
       </c>
       <c r="F63" t="s">
-        <v>6588</v>
+        <v>6777</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -100485,181 +103631,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6589</v>
+        <v>6778</v>
       </c>
       <c r="F64" t="s">
-        <v>6590</v>
+        <v>6779</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6552</v>
+        <v>6741</v>
       </c>
       <c r="F65" t="s">
-        <v>6543</v>
+        <v>6732</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6591</v>
+        <v>6780</v>
       </c>
       <c r="F66" t="s">
-        <v>6592</v>
+        <v>6781</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6593</v>
+        <v>6782</v>
       </c>
       <c r="F67" t="s">
-        <v>6594</v>
+        <v>6783</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6595</v>
+        <v>6784</v>
       </c>
       <c r="F68" t="s">
-        <v>6559</v>
+        <v>6748</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6596</v>
+        <v>6785</v>
       </c>
       <c r="F69" t="s">
-        <v>6597</v>
+        <v>6786</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6598</v>
+        <v>6787</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6599</v>
+        <v>6788</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6600</v>
+        <v>6789</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6601</v>
+        <v>6790</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6602</v>
+        <v>6791</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6603</v>
+        <v>6792</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6604</v>
+        <v>6793</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6605</v>
+        <v>6794</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6606</v>
+        <v>6795</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6607</v>
+        <v>6796</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6608</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6609</v>
+        <v>6798</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6610</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6611</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6612</v>
+        <v>6801</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6613</v>
+        <v>6802</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6614</v>
+        <v>6803</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6615</v>
+        <v>6804</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6616</v>
+        <v>6805</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6617</v>
+        <v>6806</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6356</v>
+        <v>6545</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6618</v>
+        <v>6807</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6619</v>
+        <v>6808</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6620</v>
+        <v>6809</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6621</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6622</v>
+        <v>6811</v>
       </c>
     </row>
   </sheetData>
@@ -100686,10 +103832,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6623</v>
+        <v>6812</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6624</v>
+        <v>6813</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -100698,13 +103844,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6625</v>
+        <v>6814</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>6301</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6626</v>
+        <v>6815</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -100712,13 +103858,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6627</v>
+        <v>6816</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6628</v>
+        <v>6817</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -100730,13 +103876,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6629</v>
+        <v>6818</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6630</v>
+        <v>6819</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -100747,19 +103893,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6631</v>
+        <v>6820</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6632</v>
+        <v>6821</v>
       </c>
       <c r="S10" t="s">
-        <v>6633</v>
+        <v>6822</v>
       </c>
       <c r="T10" t="s">
-        <v>6634</v>
+        <v>6823</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -100773,15 +103919,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6635</v>
+        <v>6824</v>
       </c>
       <c r="S11" t="s">
-        <v>6360</v>
+        <v>6549</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6636</v>
+        <v>6825</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -100790,18 +103936,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6637</v>
+        <v>6826</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6638</v>
+        <v>6827</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6639</v>
+        <v>6828</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -100810,7 +103956,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6640</v>
+        <v>6829</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -100821,13 +103967,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6641</v>
+        <v>6830</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6642</v>
+        <v>6831</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -100838,7 +103984,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6643</v>
+        <v>6832</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -100847,10 +103993,10 @@
         <v>3589</v>
       </c>
       <c r="S15" t="s">
-        <v>6527</v>
+        <v>6716</v>
       </c>
       <c r="T15" t="s">
-        <v>6644</v>
+        <v>6833</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -100861,12 +104007,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6645</v>
+        <v>6834</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6646</v>
+        <v>6835</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -100874,22 +104020,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6647</v>
+        <v>6836</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6648</v>
+        <v>6837</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6649</v>
+        <v>6838</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6650</v>
+        <v>6839</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6651</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -100900,39 +104046,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6652</v>
+        <v>6841</v>
       </c>
       <c r="H32" t="s">
-        <v>6653</v>
+        <v>6842</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6654</v>
+        <v>6843</v>
       </c>
       <c r="K32" t="s">
-        <v>6655</v>
+        <v>6844</v>
       </c>
       <c r="N32" t="s">
-        <v>6656</v>
+        <v>6845</v>
       </c>
       <c r="Q32" t="s">
-        <v>6657</v>
+        <v>6846</v>
       </c>
       <c r="S32" t="s">
-        <v>6384</v>
+        <v>6573</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6658</v>
+        <v>6847</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6659</v>
+        <v>6848</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -100941,13 +104087,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6660</v>
+        <v>6849</v>
       </c>
       <c r="K33" t="s">
-        <v>6661</v>
+        <v>6850</v>
       </c>
       <c r="N33" t="s">
-        <v>6662</v>
+        <v>6851</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -100955,153 +104101,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6663</v>
+        <v>6852</v>
       </c>
       <c r="K34" t="s">
-        <v>6664</v>
+        <v>6853</v>
       </c>
       <c r="N34" t="s">
-        <v>6665</v>
+        <v>6854</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6666</v>
+        <v>6855</v>
       </c>
       <c r="N35" t="s">
-        <v>6667</v>
+        <v>6856</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6668</v>
+        <v>6857</v>
       </c>
       <c r="N36" t="s">
-        <v>6669</v>
+        <v>6858</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6670</v>
+        <v>6859</v>
       </c>
       <c r="N37" t="s">
-        <v>6671</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6672</v>
+        <v>6861</v>
       </c>
       <c r="N38" t="s">
-        <v>6673</v>
+        <v>6862</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6397</v>
+        <v>6586</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6674</v>
+        <v>6863</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6675</v>
+        <v>6864</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6676</v>
+        <v>6865</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6677</v>
+        <v>6866</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6678</v>
+        <v>6867</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6679</v>
+        <v>6868</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6680</v>
+        <v>6869</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6681</v>
+        <v>6870</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6682</v>
+        <v>6871</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6683</v>
+        <v>6872</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6574</v>
+        <v>6763</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6684</v>
+        <v>6873</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6685</v>
+        <v>6874</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6572</v>
+        <v>6761</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6686</v>
+        <v>6875</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6687</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6688</v>
+        <v>6877</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6689</v>
+        <v>6878</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6690</v>
+        <v>6879</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6691</v>
+        <v>6880</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -101109,7 +104255,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6692</v>
+        <v>6881</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -101125,7 +104271,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6693</v>
+        <v>6882</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -101141,21 +104287,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6694</v>
+        <v>6883</v>
       </c>
       <c r="J68" t="s">
-        <v>6695</v>
+        <v>6884</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6696</v>
+        <v>6885</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6697</v>
+        <v>6886</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -101164,52 +104310,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6472</v>
+        <v>6661</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6698</v>
+        <v>6887</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6329</v>
+        <v>6518</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6482</v>
+        <v>6671</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6505</v>
+        <v>6694</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6699</v>
+        <v>6888</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6700</v>
+        <v>6889</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6494</v>
+        <v>6683</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6701</v>
+        <v>6890</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6702</v>
+        <v>6891</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -101271,7 +104417,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6703</v>
+        <v>6892</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -101279,10 +104425,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6704</v>
+        <v>6893</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6705</v>
+        <v>6894</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -101290,7 +104436,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6706</v>
+        <v>6895</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -101303,15 +104449,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6707</v>
+        <v>6896</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6708</v>
+        <v>6897</v>
       </c>
       <c r="F17" t="s">
-        <v>6709</v>
+        <v>6898</v>
       </c>
     </row>
     <row r="18" spans="3:8">
